--- a/data_lake/datos_diarios_preliminares/dt=2026-07-16/Temp-max-julio-26.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-07-16/Temp-max-julio-26.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\02. Datos Diarios\Tablas\Datos hidrometeorologicos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F69FDEC-A731-4B10-8341-0299831E897D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{406E136C-DDF1-48F7-A97C-16127752DD4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="355" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1073,7 +1073,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1125,6 +1125,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1213,7 +1219,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1426,6 +1432,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -9457,7 +9469,9 @@
       <c r="R5" s="57">
         <v>30.3</v>
       </c>
-      <c r="S5" s="57"/>
+      <c r="S5" s="57">
+        <v>29.9</v>
+      </c>
       <c r="T5" s="57"/>
       <c r="U5" s="57"/>
       <c r="V5" s="57"/>
@@ -9476,7 +9490,7 @@
       <c r="AI5" s="57"/>
       <c r="AJ5" s="37">
         <f>+IF(SUM($E5:$AI5)&gt;0,LOOKUP(1000,$E5:$AI5),NA())</f>
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="AK5" s="21">
         <f>+MAX($E5:$AI5)</f>
@@ -9492,13 +9506,13 @@
       <c r="AN5" s="23">
         <v>30.197371776008229</v>
       </c>
-      <c r="AO5" s="23" t="str">
+      <c r="AO5" s="23">
         <f>IF(COUNTIF(E5:AI5,"&gt;0")&gt;=15,AVERAGE(E5:AI5),"")</f>
-        <v/>
-      </c>
-      <c r="AP5" s="23" t="str">
+        <v>31.193333333333335</v>
+      </c>
+      <c r="AP5" s="23">
         <f>IF(AN5&gt;0,IFERROR(AO5-AN5,""),"")</f>
-        <v/>
+        <v>0.99596155732510638</v>
       </c>
     </row>
     <row r="6" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9556,7 +9570,9 @@
       <c r="R6" s="57">
         <v>29.7</v>
       </c>
-      <c r="S6" s="57"/>
+      <c r="S6" s="57">
+        <v>29.8</v>
+      </c>
       <c r="T6" s="57"/>
       <c r="U6" s="57"/>
       <c r="V6" s="57"/>
@@ -9575,7 +9591,7 @@
       <c r="AI6" s="57"/>
       <c r="AJ6" s="37">
         <f t="shared" ref="AJ6:AJ48" si="0">+IF(SUM($E6:$AI6)&gt;0,LOOKUP(1000,$E6:$AI6),NA())</f>
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="AK6" s="21">
         <f t="shared" ref="AK6:AK48" si="1">+MAX($E6:$AI6)</f>
@@ -9591,13 +9607,13 @@
       <c r="AN6" s="23">
         <v>30.65428039702234</v>
       </c>
-      <c r="AO6" s="23" t="str">
+      <c r="AO6" s="23">
         <f t="shared" ref="AO6:AO15" si="3">IF(COUNTIF(E6:AI6,"&gt;0")&gt;=15,AVERAGE(E6:AI6),"")</f>
-        <v/>
-      </c>
-      <c r="AP6" s="23" t="str">
+        <v>30.533333333333328</v>
+      </c>
+      <c r="AP6" s="23">
         <f t="shared" ref="AP6:AP48" si="4">IF(AN6&gt;0,IFERROR(AO6-AN6,""),"")</f>
-        <v/>
+        <v>-0.12094706368901242</v>
       </c>
     </row>
     <row r="7" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9655,7 +9671,9 @@
       <c r="R7" s="57">
         <v>37</v>
       </c>
-      <c r="S7" s="57"/>
+      <c r="S7" s="79">
+        <v>38.6</v>
+      </c>
       <c r="T7" s="57"/>
       <c r="U7" s="57"/>
       <c r="V7" s="57"/>
@@ -9674,29 +9692,29 @@
       <c r="AI7" s="57"/>
       <c r="AJ7" s="37">
         <f t="shared" si="0"/>
-        <v>37</v>
+        <v>38.6</v>
       </c>
       <c r="AK7" s="21">
         <f t="shared" si="1"/>
-        <v>38.4</v>
+        <v>38.6</v>
       </c>
       <c r="AL7" s="22">
         <v>38.4</v>
       </c>
       <c r="AM7" s="23">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="AN7" s="23">
         <v>33.366016007569073</v>
       </c>
-      <c r="AO7" s="23" t="str">
+      <c r="AO7" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP7" s="23" t="str">
+        <v>35.906666666666666</v>
+      </c>
+      <c r="AP7" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2.5406506590975937</v>
       </c>
     </row>
     <row r="8" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9754,7 +9772,9 @@
       <c r="R8" s="57">
         <v>33.6</v>
       </c>
-      <c r="S8" s="57"/>
+      <c r="S8" s="57">
+        <v>33.799999999999997</v>
+      </c>
       <c r="T8" s="57"/>
       <c r="U8" s="57"/>
       <c r="V8" s="57"/>
@@ -9773,7 +9793,7 @@
       <c r="AI8" s="57"/>
       <c r="AJ8" s="37">
         <f t="shared" si="0"/>
-        <v>33.6</v>
+        <v>33.799999999999997</v>
       </c>
       <c r="AK8" s="21">
         <f t="shared" si="1"/>
@@ -9789,13 +9809,13 @@
       <c r="AN8" s="23">
         <v>32.249043010752693</v>
       </c>
-      <c r="AO8" s="23" t="str">
+      <c r="AO8" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP8" s="23" t="str">
+        <v>33.326666666666668</v>
+      </c>
+      <c r="AP8" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.0776236559139747</v>
       </c>
     </row>
     <row r="9" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9853,7 +9873,9 @@
       <c r="R9" s="57">
         <v>35.1</v>
       </c>
-      <c r="S9" s="57"/>
+      <c r="S9" s="57">
+        <v>34.700000000000003</v>
+      </c>
       <c r="T9" s="57"/>
       <c r="U9" s="57"/>
       <c r="V9" s="57"/>
@@ -9872,7 +9894,7 @@
       <c r="AI9" s="57"/>
       <c r="AJ9" s="37">
         <f t="shared" si="0"/>
-        <v>35.1</v>
+        <v>34.700000000000003</v>
       </c>
       <c r="AK9" s="21">
         <f t="shared" si="1"/>
@@ -9888,13 +9910,13 @@
       <c r="AN9" s="23">
         <v>33.091246137683846</v>
       </c>
-      <c r="AO9" s="23" t="str">
+      <c r="AO9" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP9" s="23" t="str">
+        <v>34.026666666666664</v>
+      </c>
+      <c r="AP9" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.93542052898281725</v>
       </c>
     </row>
     <row r="10" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9952,7 +9974,9 @@
       <c r="R10" s="57">
         <v>36.700000000000003</v>
       </c>
-      <c r="S10" s="57"/>
+      <c r="S10" s="57">
+        <v>37</v>
+      </c>
       <c r="T10" s="57"/>
       <c r="U10" s="57"/>
       <c r="V10" s="57"/>
@@ -9971,7 +9995,7 @@
       <c r="AI10" s="57"/>
       <c r="AJ10" s="37">
         <f t="shared" si="0"/>
-        <v>36.700000000000003</v>
+        <v>37</v>
       </c>
       <c r="AK10" s="21">
         <f t="shared" si="1"/>
@@ -9987,13 +10011,13 @@
       <c r="AN10" s="23">
         <v>35.380238227660357</v>
       </c>
-      <c r="AO10" s="23" t="str">
+      <c r="AO10" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP10" s="23" t="str">
+        <v>35.726666666666667</v>
+      </c>
+      <c r="AP10" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.34642843900630993</v>
       </c>
     </row>
     <row r="11" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10051,7 +10075,9 @@
       <c r="R11" s="57">
         <v>40.4</v>
       </c>
-      <c r="S11" s="57"/>
+      <c r="S11" s="80">
+        <v>40.4</v>
+      </c>
       <c r="T11" s="57"/>
       <c r="U11" s="57"/>
       <c r="V11" s="57"/>
@@ -10086,13 +10112,13 @@
       <c r="AN11" s="23">
         <v>35.537284092848601</v>
       </c>
-      <c r="AO11" s="23" t="str">
+      <c r="AO11" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP11" s="23" t="str">
+        <v>38.239999999999995</v>
+      </c>
+      <c r="AP11" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2.7027159071513935</v>
       </c>
     </row>
     <row r="12" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10150,7 +10176,9 @@
       <c r="R12" s="57">
         <v>35.6</v>
       </c>
-      <c r="S12" s="57"/>
+      <c r="S12" s="57">
+        <v>36.200000000000003</v>
+      </c>
       <c r="T12" s="57"/>
       <c r="U12" s="57"/>
       <c r="V12" s="57"/>
@@ -10169,7 +10197,7 @@
       <c r="AI12" s="57"/>
       <c r="AJ12" s="37">
         <f t="shared" si="0"/>
-        <v>35.6</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK12" s="21">
         <f t="shared" si="1"/>
@@ -10185,13 +10213,13 @@
       <c r="AN12" s="23">
         <v>32.188624146173737</v>
       </c>
-      <c r="AO12" s="23" t="str">
+      <c r="AO12" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP12" s="23" t="str">
+        <v>34.840000000000003</v>
+      </c>
+      <c r="AP12" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2.6513758538262664</v>
       </c>
     </row>
     <row r="13" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10249,7 +10277,9 @@
       <c r="R13" s="57">
         <v>36</v>
       </c>
-      <c r="S13" s="57"/>
+      <c r="S13" s="57">
+        <v>37.6</v>
+      </c>
       <c r="T13" s="57"/>
       <c r="U13" s="57"/>
       <c r="V13" s="57"/>
@@ -10268,7 +10298,7 @@
       <c r="AI13" s="57"/>
       <c r="AJ13" s="37">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>37.6</v>
       </c>
       <c r="AK13" s="21">
         <f t="shared" si="1"/>
@@ -10284,13 +10314,13 @@
       <c r="AN13" s="23">
         <v>33.381792114695337</v>
       </c>
-      <c r="AO13" s="23" t="str">
+      <c r="AO13" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP13" s="23" t="str">
+        <v>36.04</v>
+      </c>
+      <c r="AP13" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2.6582078853046625</v>
       </c>
     </row>
     <row r="14" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10348,7 +10378,9 @@
       <c r="R14" s="57">
         <v>36.4</v>
       </c>
-      <c r="S14" s="57"/>
+      <c r="S14" s="57">
+        <v>37.1</v>
+      </c>
       <c r="T14" s="57"/>
       <c r="U14" s="57"/>
       <c r="V14" s="57"/>
@@ -10367,7 +10399,7 @@
       <c r="AI14" s="57"/>
       <c r="AJ14" s="37">
         <f t="shared" si="0"/>
-        <v>36.4</v>
+        <v>37.1</v>
       </c>
       <c r="AK14" s="21">
         <f t="shared" si="1"/>
@@ -10383,13 +10415,13 @@
       <c r="AN14" s="23">
         <v>33.224936599214232</v>
       </c>
-      <c r="AO14" s="23" t="str">
+      <c r="AO14" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP14" s="23" t="str">
+        <v>34.986666666666665</v>
+      </c>
+      <c r="AP14" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.761730067452433</v>
       </c>
     </row>
     <row r="15" spans="1:46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10447,7 +10479,9 @@
       <c r="R15" s="57">
         <v>32.6</v>
       </c>
-      <c r="S15" s="57"/>
+      <c r="S15" s="57">
+        <v>33.1</v>
+      </c>
       <c r="T15" s="57"/>
       <c r="U15" s="57"/>
       <c r="V15" s="57"/>
@@ -10466,7 +10500,7 @@
       <c r="AI15" s="57"/>
       <c r="AJ15" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>33.1</v>
       </c>
       <c r="AK15" s="21">
         <f t="shared" si="1"/>
@@ -10482,13 +10516,13 @@
       <c r="AN15" s="23">
         <v>31.73533745607995</v>
       </c>
-      <c r="AO15" s="23" t="str">
+      <c r="AO15" s="23">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="AP15" s="23" t="str">
+        <v>31.686666666666667</v>
+      </c>
+      <c r="AP15" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-4.8670789413282733E-2</v>
       </c>
     </row>
     <row r="16" spans="1:46" s="2" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -10595,7 +10629,9 @@
       <c r="R17" s="57">
         <v>36</v>
       </c>
-      <c r="S17" s="57"/>
+      <c r="S17" s="57">
+        <v>35.6</v>
+      </c>
       <c r="T17" s="57"/>
       <c r="U17" s="57"/>
       <c r="V17" s="57"/>
@@ -10614,7 +10650,7 @@
       <c r="AI17" s="57"/>
       <c r="AJ17" s="37">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>35.6</v>
       </c>
       <c r="AK17" s="21">
         <f t="shared" si="1"/>
@@ -10630,13 +10666,13 @@
       <c r="AN17" s="23">
         <v>32.673982202447156</v>
       </c>
-      <c r="AO17" s="23" t="str">
+      <c r="AO17" s="23">
         <f>IF(COUNTIF(E17:AI17,"&gt;0")&gt;=15,AVERAGE(E17:AI17),"")</f>
-        <v/>
-      </c>
-      <c r="AP17" s="23" t="str">
+        <v>34.273333333333326</v>
+      </c>
+      <c r="AP17" s="23">
         <f>IF(AN17&gt;0,IFERROR(AO17-AN17,""),"")</f>
-        <v/>
+        <v>1.5993511308861699</v>
       </c>
     </row>
     <row r="18" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10667,7 +10703,7 @@
       <c r="I18" s="57">
         <v>29.2</v>
       </c>
-      <c r="J18" s="57">
+      <c r="J18" s="79">
         <v>30.4</v>
       </c>
       <c r="K18" s="57">
@@ -10694,7 +10730,9 @@
       <c r="R18" s="57">
         <v>27.6</v>
       </c>
-      <c r="S18" s="57"/>
+      <c r="S18" s="57">
+        <v>30.1</v>
+      </c>
       <c r="T18" s="57"/>
       <c r="U18" s="57"/>
       <c r="V18" s="57"/>
@@ -10713,7 +10751,7 @@
       <c r="AI18" s="57"/>
       <c r="AJ18" s="37">
         <f t="shared" si="0"/>
-        <v>27.6</v>
+        <v>30.1</v>
       </c>
       <c r="AK18" s="21">
         <f t="shared" si="1"/>
@@ -10729,13 +10767,13 @@
       <c r="AN18" s="23">
         <v>26.05987085395687</v>
       </c>
-      <c r="AO18" s="23" t="str">
+      <c r="AO18" s="23">
         <f t="shared" ref="AO18:AO33" si="5">IF(COUNTIF(E18:AI18,"&gt;0")&gt;=15,AVERAGE(E18:AI18),"")</f>
-        <v/>
-      </c>
-      <c r="AP18" s="23" t="str">
+        <v>27.880000000000003</v>
+      </c>
+      <c r="AP18" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.8201291460431328</v>
       </c>
     </row>
     <row r="19" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10793,7 +10831,9 @@
       <c r="R19" s="57">
         <v>33.799999999999997</v>
       </c>
-      <c r="S19" s="57"/>
+      <c r="S19" s="57">
+        <v>35.700000000000003</v>
+      </c>
       <c r="T19" s="57"/>
       <c r="U19" s="57"/>
       <c r="V19" s="57"/>
@@ -10812,7 +10852,7 @@
       <c r="AI19" s="57"/>
       <c r="AJ19" s="37">
         <f t="shared" si="0"/>
-        <v>33.799999999999997</v>
+        <v>35.700000000000003</v>
       </c>
       <c r="AK19" s="21">
         <f t="shared" si="1"/>
@@ -10828,13 +10868,13 @@
       <c r="AN19" s="23">
         <v>33.250962402669643</v>
       </c>
-      <c r="AO19" s="23" t="str">
+      <c r="AO19" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP19" s="23" t="str">
+        <v>33.813333333333325</v>
+      </c>
+      <c r="AP19" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.5623709306636826</v>
       </c>
     </row>
     <row r="20" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10868,7 +10908,7 @@
       <c r="J20" s="57">
         <v>32</v>
       </c>
-      <c r="K20" s="57">
+      <c r="K20" s="79">
         <v>34.5</v>
       </c>
       <c r="L20" s="57">
@@ -10892,7 +10932,9 @@
       <c r="R20" s="57">
         <v>30.3</v>
       </c>
-      <c r="S20" s="57"/>
+      <c r="S20" s="57">
+        <v>31.1</v>
+      </c>
       <c r="T20" s="57"/>
       <c r="U20" s="57"/>
       <c r="V20" s="57"/>
@@ -10911,7 +10953,7 @@
       <c r="AI20" s="57"/>
       <c r="AJ20" s="37">
         <f t="shared" si="0"/>
-        <v>30.3</v>
+        <v>31.1</v>
       </c>
       <c r="AK20" s="21">
         <f t="shared" si="1"/>
@@ -10927,13 +10969,13 @@
       <c r="AN20" s="23">
         <v>28.640804597701148</v>
       </c>
-      <c r="AO20" s="23" t="str">
+      <c r="AO20" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP20" s="23" t="str">
+        <v>30.54666666666667</v>
+      </c>
+      <c r="AP20" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.9058620689655221</v>
       </c>
     </row>
     <row r="21" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10967,7 +11009,7 @@
       <c r="J21" s="57">
         <v>25.4</v>
       </c>
-      <c r="K21" s="57">
+      <c r="K21" s="79">
         <v>26.1</v>
       </c>
       <c r="L21" s="57">
@@ -10991,7 +11033,9 @@
       <c r="R21" s="57">
         <v>23.8</v>
       </c>
-      <c r="S21" s="57"/>
+      <c r="S21" s="57">
+        <v>24.4</v>
+      </c>
       <c r="T21" s="57"/>
       <c r="U21" s="57"/>
       <c r="V21" s="57"/>
@@ -11010,7 +11054,7 @@
       <c r="AI21" s="57"/>
       <c r="AJ21" s="37">
         <f t="shared" si="0"/>
-        <v>23.8</v>
+        <v>24.4</v>
       </c>
       <c r="AK21" s="21">
         <f t="shared" si="1"/>
@@ -11026,13 +11070,13 @@
       <c r="AN21" s="23">
         <v>22.609503151649971</v>
       </c>
-      <c r="AO21" s="23" t="str">
+      <c r="AO21" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP21" s="23" t="str">
+        <v>24.386666666666663</v>
+      </c>
+      <c r="AP21" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.7771635150166922</v>
       </c>
     </row>
     <row r="22" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11158,7 +11202,9 @@
       <c r="R23" s="57">
         <v>31.8</v>
       </c>
-      <c r="S23" s="57"/>
+      <c r="S23" s="57">
+        <v>29.5</v>
+      </c>
       <c r="T23" s="57"/>
       <c r="U23" s="57"/>
       <c r="V23" s="57"/>
@@ -11177,7 +11223,7 @@
       <c r="AI23" s="57"/>
       <c r="AJ23" s="37">
         <f t="shared" si="0"/>
-        <v>31.8</v>
+        <v>29.5</v>
       </c>
       <c r="AK23" s="21">
         <f t="shared" si="1"/>
@@ -11193,13 +11239,13 @@
       <c r="AN23" s="23">
         <v>26.8683870967742</v>
       </c>
-      <c r="AO23" s="23" t="str">
+      <c r="AO23" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP23" s="23" t="str">
+        <v>28.793333333333337</v>
+      </c>
+      <c r="AP23" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.924946236559137</v>
       </c>
     </row>
     <row r="24" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11257,7 +11303,9 @@
       <c r="R24" s="57">
         <v>31.4</v>
       </c>
-      <c r="S24" s="57"/>
+      <c r="S24" s="80">
+        <v>31.4</v>
+      </c>
       <c r="T24" s="57"/>
       <c r="U24" s="57"/>
       <c r="V24" s="57"/>
@@ -11292,13 +11340,13 @@
       <c r="AN24" s="23">
         <v>28.251824116743482</v>
       </c>
-      <c r="AO24" s="23" t="str">
+      <c r="AO24" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP24" s="23" t="str">
+        <v>29.993333333333332</v>
+      </c>
+      <c r="AP24" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.7415092165898507</v>
       </c>
     </row>
     <row r="25" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11356,7 +11404,9 @@
       <c r="R25" s="57">
         <v>33.200000000000003</v>
       </c>
-      <c r="S25" s="57"/>
+      <c r="S25" s="57">
+        <v>34.6</v>
+      </c>
       <c r="T25" s="57"/>
       <c r="U25" s="57"/>
       <c r="V25" s="57"/>
@@ -11375,29 +11425,29 @@
       <c r="AI25" s="57"/>
       <c r="AJ25" s="37">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>34.6</v>
       </c>
       <c r="AK25" s="21">
         <f t="shared" si="1"/>
-        <v>34</v>
+        <v>34.6</v>
       </c>
       <c r="AL25" s="22">
         <v>35.4</v>
       </c>
       <c r="AM25" s="23">
         <f t="shared" si="2"/>
-        <v>-1.3999999999999986</v>
+        <v>-0.79999999999999716</v>
       </c>
       <c r="AN25" s="23">
         <v>30.375865393221069</v>
       </c>
-      <c r="AO25" s="23" t="str">
+      <c r="AO25" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP25" s="23" t="str">
+        <v>32.260000000000005</v>
+      </c>
+      <c r="AP25" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.884134606778936</v>
       </c>
     </row>
     <row r="26" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11455,7 +11505,9 @@
       <c r="R26" s="57">
         <v>19.7</v>
       </c>
-      <c r="S26" s="57"/>
+      <c r="S26" s="57">
+        <v>19.5</v>
+      </c>
       <c r="T26" s="57"/>
       <c r="U26" s="57"/>
       <c r="V26" s="57"/>
@@ -11474,7 +11526,7 @@
       <c r="AI26" s="57"/>
       <c r="AJ26" s="37">
         <f t="shared" si="0"/>
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AK26" s="21">
         <f t="shared" si="1"/>
@@ -11490,13 +11542,13 @@
       <c r="AN26" s="23">
         <v>18.542871607443359</v>
       </c>
-      <c r="AO26" s="23" t="str">
+      <c r="AO26" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP26" s="23" t="str">
+        <v>19.453333333333333</v>
+      </c>
+      <c r="AP26" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.91046172588997365</v>
       </c>
     </row>
     <row r="27" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11554,7 +11606,9 @@
       <c r="R27" s="57">
         <v>20.399999999999999</v>
       </c>
-      <c r="S27" s="57"/>
+      <c r="S27" s="79">
+        <v>21.6</v>
+      </c>
       <c r="T27" s="57"/>
       <c r="U27" s="57"/>
       <c r="V27" s="57"/>
@@ -11573,29 +11627,29 @@
       <c r="AI27" s="57"/>
       <c r="AJ27" s="37">
         <f t="shared" si="0"/>
-        <v>20.399999999999999</v>
+        <v>21.6</v>
       </c>
       <c r="AK27" s="21">
         <f t="shared" si="1"/>
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="AL27" s="22">
         <v>21.4</v>
       </c>
       <c r="AM27" s="23">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.20000000000000284</v>
       </c>
       <c r="AN27" s="23">
         <v>16.682050544108389</v>
       </c>
-      <c r="AO27" s="23" t="str">
+      <c r="AO27" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP27" s="23" t="str">
+        <v>18.059999999999999</v>
+      </c>
+      <c r="AP27" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.3779494558916099</v>
       </c>
     </row>
     <row r="28" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11629,7 +11683,7 @@
       <c r="J28" s="57">
         <v>33.9</v>
       </c>
-      <c r="K28" s="57">
+      <c r="K28" s="79">
         <v>35.5</v>
       </c>
       <c r="L28" s="57">
@@ -11653,7 +11707,9 @@
       <c r="R28" s="57">
         <v>34.1</v>
       </c>
-      <c r="S28" s="57"/>
+      <c r="S28" s="57">
+        <v>34.6</v>
+      </c>
       <c r="T28" s="57"/>
       <c r="U28" s="57"/>
       <c r="V28" s="57"/>
@@ -11672,7 +11728,7 @@
       <c r="AI28" s="57"/>
       <c r="AJ28" s="37">
         <f t="shared" si="0"/>
-        <v>34.1</v>
+        <v>34.6</v>
       </c>
       <c r="AK28" s="21">
         <f t="shared" si="1"/>
@@ -11688,13 +11744,13 @@
       <c r="AN28" s="23">
         <v>30.528452601656159</v>
       </c>
-      <c r="AO28" s="23" t="str">
+      <c r="AO28" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP28" s="23" t="str">
+        <v>32.266666666666673</v>
+      </c>
+      <c r="AP28" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.7382140650105136</v>
       </c>
     </row>
     <row r="29" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11818,7 +11874,9 @@
       <c r="R30" s="57">
         <v>34</v>
       </c>
-      <c r="S30" s="57"/>
+      <c r="S30" s="57">
+        <v>36.200000000000003</v>
+      </c>
       <c r="T30" s="57"/>
       <c r="U30" s="57"/>
       <c r="V30" s="57"/>
@@ -11837,7 +11895,7 @@
       <c r="AI30" s="57"/>
       <c r="AJ30" s="37">
         <f t="shared" si="0"/>
-        <v>34</v>
+        <v>36.200000000000003</v>
       </c>
       <c r="AK30" s="21">
         <f t="shared" si="1"/>
@@ -11853,13 +11911,13 @@
       <c r="AN30" s="23">
         <v>33.74225089605735</v>
       </c>
-      <c r="AO30" s="23" t="str">
+      <c r="AO30" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP30" s="23" t="str">
+        <v>34.600000000000009</v>
+      </c>
+      <c r="AP30" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.85774910394265902</v>
       </c>
     </row>
     <row r="31" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11917,7 +11975,9 @@
       <c r="R31" s="57">
         <v>28.2</v>
       </c>
-      <c r="S31" s="57"/>
+      <c r="S31" s="57">
+        <v>28.6</v>
+      </c>
       <c r="T31" s="57"/>
       <c r="U31" s="57"/>
       <c r="V31" s="57"/>
@@ -11936,7 +11996,7 @@
       <c r="AI31" s="57"/>
       <c r="AJ31" s="37">
         <f t="shared" si="0"/>
-        <v>28.2</v>
+        <v>28.6</v>
       </c>
       <c r="AK31" s="21">
         <f t="shared" si="1"/>
@@ -11952,13 +12012,13 @@
       <c r="AN31" s="23">
         <v>25.387424837120619</v>
       </c>
-      <c r="AO31" s="23" t="str">
+      <c r="AO31" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP31" s="23" t="str">
+        <v>27.700000000000003</v>
+      </c>
+      <c r="AP31" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>2.3125751628793836</v>
       </c>
     </row>
     <row r="32" spans="1:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12016,7 +12076,9 @@
       <c r="R32" s="57">
         <v>17.8</v>
       </c>
-      <c r="S32" s="57"/>
+      <c r="S32" s="57">
+        <v>18.2</v>
+      </c>
       <c r="T32" s="57"/>
       <c r="U32" s="57"/>
       <c r="V32" s="57"/>
@@ -12035,7 +12097,7 @@
       <c r="AI32" s="57"/>
       <c r="AJ32" s="37">
         <f t="shared" si="0"/>
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="AK32" s="21">
         <f t="shared" si="1"/>
@@ -12051,13 +12113,13 @@
       <c r="AN32" s="27">
         <v>16.329537773261251</v>
       </c>
-      <c r="AO32" s="23" t="str">
+      <c r="AO32" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP32" s="23" t="str">
+        <v>17.853333333333335</v>
+      </c>
+      <c r="AP32" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>1.5237955600720845</v>
       </c>
     </row>
     <row r="33" spans="1:47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12115,7 +12177,9 @@
       <c r="R33" s="57">
         <v>15</v>
       </c>
-      <c r="S33" s="57"/>
+      <c r="S33" s="57">
+        <v>16</v>
+      </c>
       <c r="T33" s="57"/>
       <c r="U33" s="57"/>
       <c r="V33" s="57"/>
@@ -12134,7 +12198,7 @@
       <c r="AI33" s="57"/>
       <c r="AJ33" s="37">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK33" s="21">
         <f t="shared" si="1"/>
@@ -12150,13 +12214,13 @@
       <c r="AN33" s="23">
         <v>14.744612532443449</v>
       </c>
-      <c r="AO33" s="23" t="str">
+      <c r="AO33" s="23">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="AP33" s="23" t="str">
+        <v>15.62</v>
+      </c>
+      <c r="AP33" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.87538746755654984</v>
       </c>
       <c r="AT33" s="15"/>
     </row>
@@ -12266,7 +12330,9 @@
       <c r="R35" s="57">
         <v>33.799999999999997</v>
       </c>
-      <c r="S35" s="57"/>
+      <c r="S35" s="57">
+        <v>30.8</v>
+      </c>
       <c r="T35" s="57"/>
       <c r="U35" s="57"/>
       <c r="V35" s="57"/>
@@ -12285,7 +12351,7 @@
       <c r="AI35" s="57"/>
       <c r="AJ35" s="37">
         <f t="shared" si="0"/>
-        <v>33.799999999999997</v>
+        <v>30.8</v>
       </c>
       <c r="AK35" s="21">
         <f t="shared" si="1"/>
@@ -12301,13 +12367,13 @@
       <c r="AN35" s="23">
         <v>31.072695852534562</v>
       </c>
-      <c r="AO35" s="23" t="str">
+      <c r="AO35" s="23">
         <f>IF(COUNTIF(E35:AI35,"&gt;0")&gt;=15,AVERAGE(E35:AI35),"")</f>
-        <v/>
-      </c>
-      <c r="AP35" s="23" t="str">
+        <v>31.999999999999996</v>
+      </c>
+      <c r="AP35" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.92730414746543488</v>
       </c>
       <c r="AT35" s="15"/>
     </row>
@@ -12486,7 +12552,9 @@
       <c r="R38" s="57">
         <v>28.3</v>
       </c>
-      <c r="S38" s="57"/>
+      <c r="S38" s="57">
+        <v>32.4</v>
+      </c>
       <c r="T38" s="57"/>
       <c r="U38" s="57"/>
       <c r="V38" s="57"/>
@@ -12505,7 +12573,7 @@
       <c r="AI38" s="57"/>
       <c r="AJ38" s="37">
         <f t="shared" si="0"/>
-        <v>28.3</v>
+        <v>32.4</v>
       </c>
       <c r="AK38" s="21">
         <f t="shared" si="1"/>
@@ -12521,13 +12589,13 @@
       <c r="AN38" s="23">
         <v>30.029026223392581</v>
       </c>
-      <c r="AO38" s="23" t="str">
+      <c r="AO38" s="23">
         <f>IF(COUNTIF(E38:AI38,"&gt;0")&gt;=15,AVERAGE(E38:AI38),"")</f>
-        <v/>
-      </c>
-      <c r="AP38" s="23" t="str">
+        <v>29.766666666666662</v>
+      </c>
+      <c r="AP38" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-0.26235955672591871</v>
       </c>
       <c r="AT38" s="15"/>
     </row>
@@ -12586,7 +12654,9 @@
       <c r="R39" s="57">
         <v>33.200000000000003</v>
       </c>
-      <c r="S39" s="57"/>
+      <c r="S39" s="57">
+        <v>33.6</v>
+      </c>
       <c r="T39" s="57"/>
       <c r="U39" s="57"/>
       <c r="V39" s="57"/>
@@ -12605,29 +12675,29 @@
       <c r="AI39" s="57"/>
       <c r="AJ39" s="37">
         <f t="shared" si="0"/>
-        <v>33.200000000000003</v>
+        <v>33.6</v>
       </c>
       <c r="AK39" s="21">
         <f t="shared" si="1"/>
-        <v>33.200000000000003</v>
+        <v>33.6</v>
       </c>
       <c r="AL39" s="22">
         <v>37.4</v>
       </c>
       <c r="AM39" s="23">
         <f t="shared" si="2"/>
-        <v>-4.1999999999999957</v>
+        <v>-3.7999999999999972</v>
       </c>
       <c r="AN39" s="23">
         <v>30.843133110863921</v>
       </c>
-      <c r="AO39" s="23" t="str">
+      <c r="AO39" s="23">
         <f t="shared" ref="AO39:AO48" si="7">IF(COUNTIF(E39:AI39,"&gt;0")&gt;=15,AVERAGE(E39:AI39),"")</f>
-        <v/>
-      </c>
-      <c r="AP39" s="23" t="str">
+        <v>31.066666666666666</v>
+      </c>
+      <c r="AP39" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.22353355580274581</v>
       </c>
       <c r="AT39" s="15"/>
     </row>
@@ -12686,7 +12756,9 @@
       <c r="R40" s="57">
         <v>29.6</v>
       </c>
-      <c r="S40" s="57"/>
+      <c r="S40" s="57">
+        <v>30.6</v>
+      </c>
       <c r="T40" s="57"/>
       <c r="U40" s="57"/>
       <c r="V40" s="57"/>
@@ -12705,7 +12777,7 @@
       <c r="AI40" s="57"/>
       <c r="AJ40" s="37">
         <f t="shared" si="0"/>
-        <v>29.6</v>
+        <v>30.6</v>
       </c>
       <c r="AK40" s="21">
         <f t="shared" si="1"/>
@@ -12721,13 +12793,13 @@
       <c r="AN40" s="23">
         <v>28.947548387096781</v>
       </c>
-      <c r="AO40" s="23" t="str">
+      <c r="AO40" s="23">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AP40" s="23" t="str">
+        <v>29.24666666666667</v>
+      </c>
+      <c r="AP40" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.29911827956988901</v>
       </c>
       <c r="AT40" s="15"/>
     </row>
@@ -12786,7 +12858,9 @@
       <c r="R41" s="57">
         <v>32.6</v>
       </c>
-      <c r="S41" s="57"/>
+      <c r="S41" s="57">
+        <v>33.4</v>
+      </c>
       <c r="T41" s="57"/>
       <c r="U41" s="57"/>
       <c r="V41" s="57"/>
@@ -12805,29 +12879,29 @@
       <c r="AI41" s="57"/>
       <c r="AJ41" s="37">
         <f t="shared" si="0"/>
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
       <c r="AK41" s="21">
         <f t="shared" si="1"/>
-        <v>32.6</v>
+        <v>33.4</v>
       </c>
       <c r="AL41" s="22">
         <v>34.4</v>
       </c>
       <c r="AM41" s="23">
         <f t="shared" si="2"/>
-        <v>-1.7999999999999972</v>
+        <v>-1</v>
       </c>
       <c r="AN41" s="23">
         <v>29.366308243727591</v>
       </c>
-      <c r="AO41" s="23" t="str">
+      <c r="AO41" s="23">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AP41" s="23" t="str">
+        <v>30.106666666666669</v>
+      </c>
+      <c r="AP41" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.74035842293907805</v>
       </c>
       <c r="AT41" s="15"/>
     </row>
@@ -12947,7 +13021,9 @@
         <v>31.2</v>
       </c>
       <c r="R43" s="57"/>
-      <c r="S43" s="57"/>
+      <c r="S43" s="57">
+        <v>31.6</v>
+      </c>
       <c r="T43" s="57"/>
       <c r="U43" s="57"/>
       <c r="V43" s="57"/>
@@ -12966,7 +13042,7 @@
       <c r="AI43" s="57"/>
       <c r="AJ43" s="37">
         <f t="shared" si="0"/>
-        <v>31.2</v>
+        <v>31.6</v>
       </c>
       <c r="AK43" s="21">
         <f t="shared" si="1"/>
@@ -13045,7 +13121,9 @@
       <c r="R44" s="29">
         <v>31.2</v>
       </c>
-      <c r="S44" s="29"/>
+      <c r="S44" s="29">
+        <v>31.2</v>
+      </c>
       <c r="T44" s="29"/>
       <c r="U44" s="29"/>
       <c r="V44" s="29"/>
@@ -13145,7 +13223,9 @@
       <c r="R45" s="57">
         <v>32.799999999999997</v>
       </c>
-      <c r="S45" s="57"/>
+      <c r="S45" s="57">
+        <v>31.6</v>
+      </c>
       <c r="T45" s="57"/>
       <c r="U45" s="57"/>
       <c r="V45" s="57"/>
@@ -13164,7 +13244,7 @@
       <c r="AI45" s="57"/>
       <c r="AJ45" s="37">
         <f t="shared" si="0"/>
-        <v>32.799999999999997</v>
+        <v>31.6</v>
       </c>
       <c r="AK45" s="21">
         <f t="shared" si="1"/>
@@ -13180,13 +13260,13 @@
       <c r="AN45" s="23">
         <v>29.54581639287883</v>
       </c>
-      <c r="AO45" s="23" t="str">
+      <c r="AO45" s="23">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AP45" s="23" t="str">
+        <v>30.13333333333334</v>
+      </c>
+      <c r="AP45" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>0.58751694045450975</v>
       </c>
       <c r="AT45" s="15"/>
     </row>
@@ -13384,7 +13464,9 @@
       <c r="R48" s="57">
         <v>31.1</v>
       </c>
-      <c r="S48" s="57"/>
+      <c r="S48" s="57">
+        <v>29.2</v>
+      </c>
       <c r="T48" s="57"/>
       <c r="U48" s="57"/>
       <c r="V48" s="57"/>
@@ -13403,7 +13485,7 @@
       <c r="AI48" s="57"/>
       <c r="AJ48" s="37">
         <f t="shared" si="0"/>
-        <v>31.1</v>
+        <v>29.2</v>
       </c>
       <c r="AK48" s="21">
         <f t="shared" si="1"/>
@@ -13419,13 +13501,13 @@
       <c r="AN48" s="23">
         <v>30.34253285543608</v>
       </c>
-      <c r="AO48" s="23" t="str">
+      <c r="AO48" s="23">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="AP48" s="23" t="str">
+        <v>29.806666666666668</v>
+      </c>
+      <c r="AP48" s="23">
         <f t="shared" si="4"/>
-        <v/>
+        <v>-0.53586618876941117</v>
       </c>
     </row>
     <row r="49" spans="5:42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -14329,6 +14411,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="AM1:AM193" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="E1:AA1"/>
   </mergeCells>
@@ -26323,6 +26406,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
+    <mergeCell ref="E1:E2"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="N1:N2"/>
     <mergeCell ref="O1:O2"/>
@@ -26332,12 +26421,6 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
-    <mergeCell ref="E1:E2"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:O13 D15:O31 D33:O34 D36:O46">
     <cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="equal">
